--- a/portfolio_data_extended_v2.xlsx
+++ b/portfolio_data_extended_v2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Data Science Projects\portfolio_sql_data_project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41F7665B-DAF4-409B-82EA-86E23CB2B564}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECA6E434-E076-4D91-82BB-7F972BB04B1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38295" yWindow="0" windowWidth="38610" windowHeight="20985" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="38610" windowHeight="20985" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="securities" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="44">
   <si>
     <t>security_id</t>
   </si>
@@ -170,12 +170,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -190,8 +196,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -606,11 +613,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C101"/>
+  <dimension ref="A1:C99"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -625,14 +631,14 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
+      <c r="B2" s="1">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1">
         <v>188.76</v>
       </c>
     </row>
@@ -680,14 +686,14 @@
         <v>421.42</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+    <row r="7" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7">
+      <c r="B7" s="1">
+        <v>1</v>
+      </c>
+      <c r="C7" s="1">
         <v>185.85</v>
       </c>
     </row>
@@ -724,7 +730,7 @@
         <v>234.45</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>21</v>
       </c>
@@ -735,14 +741,14 @@
         <v>435.51</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+    <row r="12" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B12">
-        <v>1</v>
-      </c>
-      <c r="C12">
+      <c r="B12" s="1">
+        <v>1</v>
+      </c>
+      <c r="C12" s="1">
         <v>183.96</v>
       </c>
     </row>
@@ -795,10 +801,10 @@
         <v>23</v>
       </c>
       <c r="B17">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C17">
-        <v>187.01</v>
+        <v>487.99</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -806,10 +812,10 @@
         <v>23</v>
       </c>
       <c r="B18">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C18">
-        <v>332.37</v>
+        <v>227.03</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -817,32 +823,32 @@
         <v>23</v>
       </c>
       <c r="B19">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C19">
-        <v>487.99</v>
+        <v>427.31</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B20">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C20">
-        <v>227.03</v>
+        <v>185.44</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B21">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C21">
-        <v>427.31</v>
+        <v>339.77</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -850,10 +856,10 @@
         <v>24</v>
       </c>
       <c r="B22">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C22">
-        <v>185.44</v>
+        <v>475.97</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -861,10 +867,10 @@
         <v>24</v>
       </c>
       <c r="B23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C23">
-        <v>339.77</v>
+        <v>231.21</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -872,32 +878,32 @@
         <v>24</v>
       </c>
       <c r="B24">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C24">
-        <v>475.97</v>
+        <v>424</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B25">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C25">
-        <v>231.21</v>
+        <v>187.27</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B26">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C26">
-        <v>424</v>
+        <v>328.11</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -905,10 +911,10 @@
         <v>25</v>
       </c>
       <c r="B27">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C27">
-        <v>187.27</v>
+        <v>487.04</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -916,10 +922,10 @@
         <v>25</v>
       </c>
       <c r="B28">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C28">
-        <v>328.11</v>
+        <v>236.18</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -927,32 +933,32 @@
         <v>25</v>
       </c>
       <c r="B29">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C29">
-        <v>487.04</v>
+        <v>437.72</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B30">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C30">
-        <v>236.18</v>
+        <v>187.47</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B31">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C31">
-        <v>437.72</v>
+        <v>327.73</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -960,10 +966,10 @@
         <v>26</v>
       </c>
       <c r="B32">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C32">
-        <v>187.47</v>
+        <v>473.3</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -971,10 +977,10 @@
         <v>26</v>
       </c>
       <c r="B33">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C33">
-        <v>327.73</v>
+        <v>233.62</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -982,32 +988,32 @@
         <v>26</v>
       </c>
       <c r="B34">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C34">
-        <v>473.3</v>
+        <v>430.41</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B35">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C35">
-        <v>233.62</v>
+        <v>188.09</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B36">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C36">
-        <v>430.41</v>
+        <v>338.16</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -1015,10 +1021,10 @@
         <v>27</v>
       </c>
       <c r="B37">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C37">
-        <v>188.09</v>
+        <v>487.42</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -1026,10 +1032,10 @@
         <v>27</v>
       </c>
       <c r="B38">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C38">
-        <v>338.16</v>
+        <v>231.69</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
@@ -1037,32 +1043,32 @@
         <v>27</v>
       </c>
       <c r="B39">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C39">
-        <v>487.42</v>
+        <v>424.32</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B40">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C40">
-        <v>231.69</v>
+        <v>186.42</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B41">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C41">
-        <v>424.32</v>
+        <v>335.34</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
@@ -1070,10 +1076,10 @@
         <v>28</v>
       </c>
       <c r="B42">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C42">
-        <v>186.42</v>
+        <v>484.66</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
@@ -1081,10 +1087,10 @@
         <v>28</v>
       </c>
       <c r="B43">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C43">
-        <v>335.34</v>
+        <v>232.15</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -1092,32 +1098,32 @@
         <v>28</v>
       </c>
       <c r="B44">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C44">
-        <v>484.66</v>
+        <v>420.86</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B45">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C45">
-        <v>232.15</v>
+        <v>186.65</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B46">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C46">
-        <v>420.86</v>
+        <v>330.66</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
@@ -1125,10 +1131,10 @@
         <v>29</v>
       </c>
       <c r="B47">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C47">
-        <v>186.65</v>
+        <v>473.08</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
@@ -1136,10 +1142,10 @@
         <v>29</v>
       </c>
       <c r="B48">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C48">
-        <v>330.66</v>
+        <v>235.34</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
@@ -1147,32 +1153,32 @@
         <v>29</v>
       </c>
       <c r="B49">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C49">
-        <v>473.08</v>
+        <v>427.51</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B50">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C50">
-        <v>235.34</v>
+        <v>190.49</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B51">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C51">
-        <v>427.51</v>
+        <v>325.98</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
@@ -1180,10 +1186,10 @@
         <v>30</v>
       </c>
       <c r="B52">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C52">
-        <v>190.49</v>
+        <v>492.25</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
@@ -1191,10 +1197,10 @@
         <v>30</v>
       </c>
       <c r="B53">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C53">
-        <v>325.98</v>
+        <v>235.08</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
@@ -1202,32 +1208,32 @@
         <v>30</v>
       </c>
       <c r="B54">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C54">
-        <v>492.25</v>
+        <v>433.15</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B55">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C55">
-        <v>235.08</v>
+        <v>184.49</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B56">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C56">
-        <v>433.15</v>
+        <v>339.26</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
@@ -1235,10 +1241,10 @@
         <v>31</v>
       </c>
       <c r="B57">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C57">
-        <v>184.49</v>
+        <v>478.36</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
@@ -1246,10 +1252,10 @@
         <v>31</v>
       </c>
       <c r="B58">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C58">
-        <v>339.26</v>
+        <v>229.75</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
@@ -1257,32 +1263,32 @@
         <v>31</v>
       </c>
       <c r="B59">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C59">
-        <v>478.36</v>
+        <v>434.65</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B60">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C60">
-        <v>229.75</v>
+        <v>186.33</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B61">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C61">
-        <v>434.65</v>
+        <v>335.46</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
@@ -1290,10 +1296,10 @@
         <v>32</v>
       </c>
       <c r="B62">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C62">
-        <v>186.33</v>
+        <v>477.57</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
@@ -1301,10 +1307,10 @@
         <v>32</v>
       </c>
       <c r="B63">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C63">
-        <v>335.46</v>
+        <v>231.17</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
@@ -1312,32 +1318,32 @@
         <v>32</v>
       </c>
       <c r="B64">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C64">
-        <v>477.57</v>
+        <v>422.8</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B65">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C65">
-        <v>231.17</v>
+        <v>187.82</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B66">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C66">
-        <v>422.8</v>
+        <v>328.42</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
@@ -1345,10 +1351,10 @@
         <v>33</v>
       </c>
       <c r="B67">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C67">
-        <v>187.82</v>
+        <v>491.04</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
@@ -1356,10 +1362,10 @@
         <v>33</v>
       </c>
       <c r="B68">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C68">
-        <v>328.42</v>
+        <v>233.34</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
@@ -1367,32 +1373,32 @@
         <v>33</v>
       </c>
       <c r="B69">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C69">
-        <v>491.04</v>
+        <v>429.49</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B70">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C70">
-        <v>233.34</v>
+        <v>187.16</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B71">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C71">
-        <v>429.49</v>
+        <v>334.97</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
@@ -1400,10 +1406,10 @@
         <v>34</v>
       </c>
       <c r="B72">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C72">
-        <v>187.16</v>
+        <v>472.31</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
@@ -1411,10 +1417,10 @@
         <v>34</v>
       </c>
       <c r="B73">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C73">
-        <v>334.97</v>
+        <v>232.92</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
@@ -1422,32 +1428,32 @@
         <v>34</v>
       </c>
       <c r="B74">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C74">
-        <v>472.31</v>
+        <v>437.34</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B75">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C75">
-        <v>232.92</v>
+        <v>185.43</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B76">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C76">
-        <v>437.34</v>
+        <v>325.94</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
@@ -1455,10 +1461,10 @@
         <v>35</v>
       </c>
       <c r="B77">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C77">
-        <v>185.43</v>
+        <v>491.61</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
@@ -1466,10 +1472,10 @@
         <v>35</v>
       </c>
       <c r="B78">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C78">
-        <v>325.94</v>
+        <v>233.33</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
@@ -1477,32 +1483,32 @@
         <v>35</v>
       </c>
       <c r="B79">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C79">
-        <v>491.61</v>
+        <v>419.39</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B80">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C80">
-        <v>233.33</v>
+        <v>188.69</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B81">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C81">
-        <v>419.39</v>
+        <v>337.67</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
@@ -1510,10 +1516,10 @@
         <v>36</v>
       </c>
       <c r="B82">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C82">
-        <v>188.69</v>
+        <v>494.36</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
@@ -1521,10 +1527,10 @@
         <v>36</v>
       </c>
       <c r="B83">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C83">
-        <v>337.67</v>
+        <v>233.02</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
@@ -1532,32 +1538,32 @@
         <v>36</v>
       </c>
       <c r="B84">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C84">
-        <v>494.36</v>
+        <v>418.21</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B85">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C85">
-        <v>233.02</v>
+        <v>185.04</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B86">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C86">
-        <v>418.21</v>
+        <v>338.21</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
@@ -1565,10 +1571,10 @@
         <v>37</v>
       </c>
       <c r="B87">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C87">
-        <v>185.04</v>
+        <v>486.12</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
@@ -1576,10 +1582,10 @@
         <v>37</v>
       </c>
       <c r="B88">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C88">
-        <v>338.21</v>
+        <v>228.66</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
@@ -1587,32 +1593,32 @@
         <v>37</v>
       </c>
       <c r="B89">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C89">
-        <v>486.12</v>
+        <v>432.08</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B90">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C90">
-        <v>228.66</v>
+        <v>183.94</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B91">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C91">
-        <v>432.08</v>
+        <v>324.11</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
@@ -1620,10 +1626,10 @@
         <v>38</v>
       </c>
       <c r="B92">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C92">
-        <v>183.94</v>
+        <v>483.57</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
@@ -1631,10 +1637,10 @@
         <v>38</v>
       </c>
       <c r="B93">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C93">
-        <v>324.11</v>
+        <v>227.59</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
@@ -1642,32 +1648,32 @@
         <v>38</v>
       </c>
       <c r="B94">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C94">
-        <v>483.57</v>
+        <v>433</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B95">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C95">
-        <v>227.59</v>
+        <v>187.55</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B96">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C96">
-        <v>433</v>
+        <v>334.69</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
@@ -1675,10 +1681,10 @@
         <v>39</v>
       </c>
       <c r="B97">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C97">
-        <v>187.55</v>
+        <v>487.48</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
@@ -1686,10 +1692,10 @@
         <v>39</v>
       </c>
       <c r="B98">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C98">
-        <v>334.69</v>
+        <v>236.62</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
@@ -1697,31 +1703,9 @@
         <v>39</v>
       </c>
       <c r="B99">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C99">
-        <v>487.48</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A100" t="s">
-        <v>39</v>
-      </c>
-      <c r="B100">
-        <v>4</v>
-      </c>
-      <c r="C100">
-        <v>236.62</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A101" t="s">
-        <v>39</v>
-      </c>
-      <c r="B101">
-        <v>5</v>
-      </c>
-      <c r="C101">
         <v>424.95</v>
       </c>
     </row>
